--- a/02-lead-list/inboxkit-leads.xlsx
+++ b/02-lead-list/inboxkit-leads.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -484,84 +484,96 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tier A</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tier A is unreachable because headcount and techstack cannot be sourced free.</t>
+          <t>$0. Nothing was sent and no paid API was called; config/scale.md has the detail.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Tier A</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Verified-valid contacts that passed every ICP check, highest score first. (39 rows)</t>
+          <t>Tier A is unreachable because headcount and techstack cannot be sourced free.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Needs contact</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Accounts that passed every ICP check but have no verified contact yet. (2 rows)</t>
+          <t>Verified-valid contacts that passed every ICP check, highest score first. (39 rows)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Held</t>
+          <t>Needs contact</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Catch-all addresses, held back until a second check. (8 rows)</t>
+          <t>Accounts that passed every ICP check but have no verified contact yet. (2 rows)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rejects</t>
+          <t>Held</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Duplicates, rows that failed an ICP check, and bad emails, each with a reason. (43 rows)</t>
+          <t>Catch-all addresses, held back until a second check. (8 rows)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Suppressed</t>
+          <t>Rejects</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Customers, competitors and opt-outs, with the rule that matched. (8 rows)</t>
+          <t>Duplicates, rows that failed an ICP check, and bad emails, each with a reason. (43 rows)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Suppressed</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Customers, competitors and opt-outs, with the rule that matched. (8 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Run log</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>One row per pipeline run: counts, mode, credits, seconds. It holds every run since the repo was started, including development runs; the final run is the last row. (65 rows)</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>One row per pipeline run: counts, mode, credits, seconds. It holds every run since the repo was started, including development runs; the final run is the last row. (73 rows)</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -11763,6 +11775,430 @@
       </c>
       <c r="O66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-25T14:55:43+00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>icp_jobchangers.yaml</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>15</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>12</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>6</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-25T14:55:44+00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>icp.yaml</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8</v>
+      </c>
+      <c r="G68" t="n">
+        <v>21</v>
+      </c>
+      <c r="H68" t="n">
+        <v>73</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>14</v>
+      </c>
+      <c r="K68" t="n">
+        <v>8</v>
+      </c>
+      <c r="L68" t="n">
+        <v>39</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-25T17:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>icp.yaml</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>100</v>
+      </c>
+      <c r="E69" t="n">
+        <v>8</v>
+      </c>
+      <c r="F69" t="n">
+        <v>8</v>
+      </c>
+      <c r="G69" t="n">
+        <v>21</v>
+      </c>
+      <c r="H69" t="n">
+        <v>73</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" t="n">
+        <v>14</v>
+      </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L69" t="n">
+        <v>39</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-25T17:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>icp_try.yaml</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="n">
+        <v>8</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>61</v>
+      </c>
+      <c r="H70" t="n">
+        <v>24</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>14</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-25T17:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>icp_try.yaml</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>100</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>35</v>
+      </c>
+      <c r="H71" t="n">
+        <v>56</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" t="n">
+        <v>10</v>
+      </c>
+      <c r="K71" t="n">
+        <v>6</v>
+      </c>
+      <c r="L71" t="n">
+        <v>31</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-25T17:07:03+00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>icp.yaml</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>100</v>
+      </c>
+      <c r="E72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8</v>
+      </c>
+      <c r="G72" t="n">
+        <v>21</v>
+      </c>
+      <c r="H72" t="n">
+        <v>73</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>14</v>
+      </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
+      <c r="L72" t="n">
+        <v>39</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-25T17:10:25+00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>icp_jobchangers.yaml</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>15</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>12</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>6</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-25T17:10:26+00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>icp.yaml</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>100</v>
+      </c>
+      <c r="E74" t="n">
+        <v>8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8</v>
+      </c>
+      <c r="G74" t="n">
+        <v>21</v>
+      </c>
+      <c r="H74" t="n">
+        <v>73</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>14</v>
+      </c>
+      <c r="K74" t="n">
+        <v>8</v>
+      </c>
+      <c r="L74" t="n">
+        <v>39</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
